--- a/outputs/evaluation/CF_M05_req_eval_llm_report.xlsx
+++ b/outputs/evaluation/CF_M05_req_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,7 +481,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The system shall validate user credentials and grant access to the portal upon successful authentication.</t>
+          <t>The system shall validate user credentials and grant access to the portal if they are valid.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.4742</v>
+        <v>0.3083</v>
       </c>
     </row>
     <row r="3">
@@ -524,7 +524,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The system shall only show applications to which the user has authorized access.</t>
+          <t>The system shall display a list of applications corresponding to the user's access permissions upon login.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -547,16 +547,16 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CF_M05_R02</t>
+          <t>CF_M05_R23</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>View the portal applications to which the user has access.</t>
+          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.5284</v>
+        <v>0.2906</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.2504</v>
+        <v>0.2606</v>
       </c>
     </row>
     <row r="5">
@@ -610,7 +610,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The system shall verify user roles and permissions to allow or deny access to specific screens and actions.</t>
+          <t>The system shall verify user roles and permissions to allow or deny access to specific screens and data actions.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -633,16 +633,16 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M05_R23</t>
+          <t>CF_M05_R04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
+          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.2711</v>
+        <v>0.2685</v>
       </c>
     </row>
     <row r="6">
@@ -653,7 +653,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The system shall prevent access to data belonging to other clients.</t>
+          <t>Restrict access between clients.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -672,16 +672,16 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>CF_M05_R25</t>
+          <t>CF_M05_R04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>No user can access data from other customers.</t>
+          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0.2492</v>
+        <v>0.1801</v>
       </c>
     </row>
     <row r="7">
@@ -692,7 +692,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The system shall verify the client associated with the user and only display data belonging to that client.</t>
+          <t>The system shall ensure that users can only access data associated with their specific client.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.193</v>
+        <v>0.2713</v>
       </c>
     </row>
     <row r="8">
@@ -767,23 +767,23 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.4698</v>
+        <v>0.4602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R_13</t>
+          <t>R_14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The system shall allow administrators to assign or revoke application access for users.</t>
+          <t>The system shall update the user's access list upon administrator confirmation, reflecting changes in the portal.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>criterion</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -793,63 +793,24 @@
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>R_13</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CF_M05_R07</t>
+          <t>CF_M05_R03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Give or remove access to applications from users.</t>
+          <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.2619</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>R_14</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>The system shall update the user's application access list upon administrator modification.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>R_13</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CF_M05_R03</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Access the applications to which the user has access on the portal.</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>0.2483</v>
+        <v>0.2565</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/evaluation/CF_M05_req_eval_llm_report.xlsx
+++ b/outputs/evaluation/CF_M05_req_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,341 +476,40 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R_02</t>
+          <t>R_09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The system shall validate user credentials and grant access to the portal if they are valid.</t>
+          <t>Restrict access between clients.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>criterion</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>R_01</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CF_M05_R01</t>
+          <t>CF_M05_R03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Access the portal using credential authentication personal.</t>
+          <t>Access the applications to which the user has access on the portal.</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.3083</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>R_04</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>The system shall display a list of applications corresponding to the user's access permissions upon login.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>R_03</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>CF_M05_R23</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>0.2906</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>R_06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>The system shall redirect the user to the main page of the selected application.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>R_05</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>CF_M05_R08</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>The new content must maintain visual consistency with the design of the old version of the application.</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2606</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>R_08</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>The system shall verify user roles and permissions to allow or deny access to specific screens and data actions.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>R_07</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>CF_M05_R04</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2685</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>R_09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Restrict access between clients.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CF_M05_R04</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Restrict actions (create, modify and delete) on data according to the roles assigned to the user.</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>0.1801</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>R_10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>The system shall ensure that users can only access data associated with their specific client.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>R_09</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CF_M05_R23</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>The system must have a secure authentication mechanism and permission verification to ensure that each user can only access the information and functionalities that correspond to it.</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>0.2713</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>R_12</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>The system shall display the new name in all screens and data where the old name was mentioned.</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>R_11</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CF_M05_R06</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Convert any mention of the old name to the new name.</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>0.4602</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>R_14</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>The system shall update the user's access list upon administrator confirmation, reflecting changes in the portal.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>criterion</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>R_13</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CF_M05_R03</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Access the applications to which the user has access on the portal.</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2565</v>
+        <v>0.1895</v>
       </c>
     </row>
   </sheetData>
